--- a/02-PORTFOLIO-THEORY/M05/BUS331_Returns_Student_Template.xlsx
+++ b/02-PORTFOLIO-THEORY/M05/BUS331_Returns_Student_Template.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 HPR basics" sheetId="1" r:id="R7501d8e8d5894338"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 Stock HPR" sheetId="2" r:id="R21871839cff848ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 Annualize stock HPR" sheetId="3" r:id="Ra0d237a59c074605"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 Compare annual returns" sheetId="4" r:id="R9b2cd691c7564d58"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05 APR" sheetId="5" r:id="R4ce10bd0c8e94932"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06 EAR" sheetId="6" r:id="R7eae554c64614787"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07 Continuous" sheetId="7" r:id="R8b8b19626e5c443b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08 Rate use cases" sheetId="8" r:id="R7175f1714d3c47fd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09 Arithmetic" sheetId="9" r:id="R9bec107179bf45bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10 Geometric" sheetId="10" r:id="R2be9f855294d4cd3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11 Wealth HPR annualized" sheetId="11" r:id="Rb638daea8bb542e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 IRR worked example" sheetId="12" r:id="Rb9ec52cb37a84b86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13 Q3 Waylan" sheetId="13" r:id="R64883ae78f194b26"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14 Q5 cash flows" sheetId="14" r:id="Rbf001a58d94d4f7c"/>
-  </x:sheets>
-</x:workbook>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheets>
+    <sheet name="01 HPR basics" sheetId="1" r:id="R7501d8e8d5894338"/>
+    <sheet name="02 Stock HPR" sheetId="2" r:id="R21871839cff848ce"/>
+    <sheet name="03 Annualize stock HPR" sheetId="3" r:id="Ra0d237a59c074605"/>
+    <sheet name="04 Compare annual returns" sheetId="4" r:id="R9b2cd691c7564d58"/>
+    <sheet name="05 EAR" sheetId="6" r:id="R7eae554c64614787"/>
+    <sheet name="06 APR" sheetId="5" r:id="R4ce10bd0c8e94932"/>
+    <sheet name="07 Continuous" sheetId="7" r:id="R8b8b19626e5c443b"/>
+    <sheet name="08 Rate use cases" sheetId="8" r:id="R7175f1714d3c47fd"/>
+    <sheet name="09 Wealth HPR annualized" sheetId="11" r:id="Rb638daea8bb542e9"/>
+    <sheet name="10 Arithmetic" sheetId="9" r:id="R9bec107179bf45bc"/>
+    <sheet name="11 Geometric" sheetId="10" r:id="R2be9f855294d4cd3"/>
+    <sheet name="12 Q3 Waylan" sheetId="13" r:id="R64883ae78f194b26"/>
+    <sheet name="13 IRR worked example" sheetId="12" r:id="Rb9ec52cb37a84b86"/>
+    <sheet name="14 Q5 cash flows" sheetId="14" r:id="Rbf001a58d94d4f7c"/>
+  </sheets>
+</workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
